--- a/artfynd/A 18425-2025 artfynd.xlsx
+++ b/artfynd/A 18425-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115434859</v>
+        <v>115434469</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallön (Kallön), Upl</t>
+          <t>Kallön, Kallön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620940</v>
+        <v>621067</v>
       </c>
       <c r="R2" t="n">
-        <v>6655291</v>
+        <v>6655380</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,12 +785,7 @@
         <v>115434653</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallön (Kallön), Upl</t>
+          <t>Kallön, Kallön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -914,53 +889,63 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115434469</v>
+        <v>115434859</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallön (Kallön), Upl</t>
+          <t>Kallön, Kallön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621067</v>
+        <v>620940</v>
       </c>
       <c r="R4" t="n">
-        <v>6655380</v>
+        <v>6655291</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
